--- a/document/协会现有成员信息表.xlsx
+++ b/document/协会现有成员信息表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project_Document\Python\pycharm\Application\personalwebsite\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project_Document\GitHub\presonalwebsite\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443D0E5F-3702-4168-BC26-D9F1D06D4E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DFC540-2932-43C6-863C-12AAD95E86A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
